--- a/Bao cao/HPG/HPG_Model_2026-06.xlsx
+++ b/Bao cao/HPG/HPG_Model_2026-06.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>30/06/2026 22:10</t>
+          <t>30/06/2026 23:03</t>
         </is>
       </c>
     </row>

--- a/Bao cao/HPG/HPG_Model_2026-06.xlsx
+++ b/Bao cao/HPG/HPG_Model_2026-06.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_Revenue_Model" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_PnL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_Balance_Sheet" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_Cash_Flow" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_Valuation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_Hist_Multiples" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_Sensitivity" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_PESTLE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_Leading_Indicators" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_Investment_Thesis" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_Summary_Snapshot" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_Steel_Analysis" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_Quarterly_Data" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="16_Steel_Accounting" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="17_Gia_Hang_Hoa" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Revenue_Model" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_PnL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Balance_Sheet" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Cash_Flow" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Valuation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Hist_Multiples" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Sensitivity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_PESTLE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Leading_Indicators" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Investment_Thesis" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Summary_Snapshot" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Steel_Analysis" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_Quarterly_Data" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_Steel_Accounting" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_Gia_Hang_Hoa" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -611,10 +611,10 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="31" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="31" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="32" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -712,13 +712,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -741,7 +741,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="18000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
                 <a:srgbClr val="1F4E79"/>
               </a:solidFill>
@@ -751,7 +751,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -776,7 +776,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="18000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
                 <a:srgbClr val="FF8C00"/>
               </a:solidFill>
@@ -786,7 +786,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -831,8 +831,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -858,13 +858,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -887,7 +887,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="18000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
                 <a:srgbClr val="E74C3C"/>
               </a:solidFill>
@@ -897,7 +897,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -942,8 +942,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -969,13 +969,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -998,7 +998,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="18000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
                 <a:srgbClr val="27AE60"/>
               </a:solidFill>
@@ -1008,7 +1008,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1053,8 +1053,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1080,14 +1080,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1111,10 +1111,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1F4E79"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1138,7 +1138,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1162,7 +1162,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1186,7 +1186,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1210,7 +1210,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1234,7 +1234,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1258,7 +1258,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1282,7 +1282,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1306,7 +1306,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1331,7 +1331,7 @@
           <idx val="9"/>
           <order val="9"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
                 <a:srgbClr val="E74C3C"/>
               </a:solidFill>
@@ -1341,7 +1341,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1364,8 +1364,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1391,8 +1391,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1418,14 +1418,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1443,7 +1443,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
                 <a:srgbClr val="1F4E79"/>
               </a:solidFill>
@@ -1453,7 +1453,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1473,7 +1473,7 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
                 <a:srgbClr val="E74C3C"/>
               </a:solidFill>
@@ -1483,7 +1483,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1503,7 +1503,7 @@
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
                 <a:srgbClr val="27AE60"/>
               </a:solidFill>
@@ -1513,7 +1513,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1553,8 +1553,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1580,14 +1580,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1610,7 +1610,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="1F4E79"/>
               </a:solidFill>
@@ -1620,7 +1620,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1645,7 +1645,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="E74C3C"/>
               </a:solidFill>
@@ -1655,7 +1655,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1680,14 +1680,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1712,14 +1712,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1744,14 +1744,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1776,14 +1776,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1808,14 +1808,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1840,14 +1840,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1872,14 +1872,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1904,14 +1904,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1936,14 +1936,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1968,14 +1968,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2000,14 +2000,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2032,14 +2032,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2084,8 +2084,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2113,7 +2113,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -2128,9 +2128,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2150,9 +2150,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2172,9 +2172,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2184,7 +2184,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -2199,9 +2199,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2221,9 +2221,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2233,7 +2233,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -2248,9 +2248,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>02/07/2026 23:27</t>
+          <t>03/07/2026 10:11</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B5" s="62" t="inlineStr">
         <is>
-          <t>Tài chính: D/E 0.65x an toàn. ROE TTM 16.5%. FCF cải thiện nhờ DQ2 vận hành. Biên LNG phục hồi từ 10.9% (2023) lên ~15.9% (2026E).</t>
+          <t>Tài chính: D/E 0.65x an toàn. ROE TTM 16.5%. FCF cải thiện nhờ DQ2 vận hành. Biên LNG phục hồi từ 10.9% (2023) lên ~15.6% (2026E).</t>
         </is>
       </c>
       <c r="C5" s="64" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>+13,308 tỷ</t>
+          <t>+12,759 tỷ</t>
         </is>
       </c>
       <c r="C31" s="74" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>169,424 tỷ</t>
+          <t>168,875 tỷ</t>
         </is>
       </c>
       <c r="C33" s="74" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="C38" s="74" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>+5,757 tỷ</t>
+          <t>+5,252 tỷ</t>
         </is>
       </c>
       <c r="C41" s="74" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B43" s="35" t="inlineStr">
         <is>
-          <t>21,210 tỷ</t>
+          <t>20,705 tỷ</t>
         </is>
       </c>
       <c r="C43" s="74" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="B43" s="35" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="C43" s="35" t="inlineStr">
         <is>
-          <t>KH 2026E NI: 21,210 tỷ</t>
+          <t>KH 2026E NI: 20,705 tỷ</t>
         </is>
       </c>
       <c r="D43" s="35" t="inlineStr">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B14" s="62" t="inlineStr">
         <is>
-          <t>Giá HRC 470→475 USD/tấn. Spread 150 USD/tấn (2026E) từ 128 USD/tấn (2025)</t>
+          <t>Giá HRC 470→468 USD/tấn. Spread 146 USD/tấn (2026E) từ 128 USD/tấn (2025)</t>
         </is>
       </c>
       <c r="C14" s="92" t="inlineStr">
@@ -12224,7 +12224,7 @@
         <is>
           <t>Đánh giá tổng thể: HPG ĐÃ SẴN SÀNG CHO GIAI ĐOẠN HÁI QUẢ.
 • Vĩ mô đảo chiều ✅: Lãi suất giảm, đầu tư công tăng, BĐS phục hồi.
-• Spread nở ra ✅: Giá HRC hồi phục từ 618 (2023) lên 475 (2026E), Spread 182→150 USD/tấn.
+• Spread nở ra ✅: Giá HRC hồi phục từ 618 (2023) lên 468 (2026E), Spread 182→146 USD/tấn.
 • Tồn kho giá rẻ ✅: Quặng 105 USD/tấn (thấp nhất 5 năm) → lợi thế GM Q2-Q4/2026.
 • DQ2 hoàn thành ✅: CIP giảm mạnh, FCF sẽ chuyển dương từ 2026.
 Kết luận: HPG đang bước vào chu kỳ lợi nhuận tăng mạnh (2026-2028) nhờ hội tụ đủ 4 yếu tố. Đây là thời điểm lý tưởng để nắm giữ cổ phiếu thép chu kỳ.</t>
@@ -12379,28 +12379,28 @@
         </is>
       </c>
       <c r="G5" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H5" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I5" s="108">
+        <v>709.2</v>
+      </c>
+      <c r="H5" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I5" s="107">
         <f>G5-1.6*C5-0.6*D5-100</f>
         <v/>
       </c>
-      <c r="J5" s="107" t="inlineStr">
+      <c r="J5" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="107" t="inlineStr">
+      <c r="K5" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="107" t="inlineStr">
+      <c r="L5" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12431,28 +12431,28 @@
         </is>
       </c>
       <c r="G6" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H6" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I6" s="108">
+        <v>737.8</v>
+      </c>
+      <c r="H6" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I6" s="107">
         <f>G6-1.6*C5-0.6*D5-100</f>
         <v/>
       </c>
-      <c r="J6" s="107" t="inlineStr">
+      <c r="J6" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="107" t="inlineStr">
+      <c r="K6" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L6" s="107" t="inlineStr">
+      <c r="L6" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12483,28 +12483,28 @@
         </is>
       </c>
       <c r="G7" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H7" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I7" s="108">
+        <v>803.2</v>
+      </c>
+      <c r="H7" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I7" s="107">
         <f>G7-1.6*C6-0.6*D6-100</f>
         <v/>
       </c>
-      <c r="J7" s="107" t="inlineStr">
+      <c r="J7" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K7" s="107" t="inlineStr">
+      <c r="K7" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="107" t="inlineStr">
+      <c r="L7" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12535,28 +12535,28 @@
         </is>
       </c>
       <c r="G8" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H8" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I8" s="108">
+        <v>672.7</v>
+      </c>
+      <c r="H8" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I8" s="107">
         <f>G8-1.6*C7-0.6*D7-100</f>
         <v/>
       </c>
-      <c r="J8" s="107" t="inlineStr">
+      <c r="J8" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="107" t="inlineStr">
+      <c r="K8" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L8" s="107" t="inlineStr">
+      <c r="L8" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12587,28 +12587,28 @@
         </is>
       </c>
       <c r="G9" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H9" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I9" s="108">
+        <v>664.9</v>
+      </c>
+      <c r="H9" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I9" s="107">
         <f>G9-1.6*C8-0.6*D8-100</f>
         <v/>
       </c>
-      <c r="J9" s="107" t="inlineStr">
+      <c r="J9" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="107" t="inlineStr">
+      <c r="K9" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="107" t="inlineStr">
+      <c r="L9" s="108" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12639,14 +12639,14 @@
         </is>
       </c>
       <c r="G10" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H10" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I10" s="108">
+        <v>706.9</v>
+      </c>
+      <c r="H10" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I10" s="107">
         <f>G10-1.6*C9-0.6*D9-100</f>
         <v/>
       </c>
@@ -12688,14 +12688,14 @@
         </is>
       </c>
       <c r="G11" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H11" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I11" s="108">
+        <v>623.2</v>
+      </c>
+      <c r="H11" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I11" s="107">
         <f>G11-1.6*C10-0.6*D10-100</f>
         <v/>
       </c>
@@ -12737,14 +12737,14 @@
         </is>
       </c>
       <c r="G12" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H12" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I12" s="108">
+        <v>564.5</v>
+      </c>
+      <c r="H12" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I12" s="107">
         <f>G12-1.6*C11-0.6*D11-100</f>
         <v/>
       </c>
@@ -12786,14 +12786,14 @@
         </is>
       </c>
       <c r="G13" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H13" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I13" s="108">
+        <v>594</v>
+      </c>
+      <c r="H13" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I13" s="107">
         <f>G13-1.6*C12-0.6*D12-100</f>
         <v/>
       </c>
@@ -12837,12 +12837,12 @@
       <c r="G14" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="H14" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I14" s="108">
+      <c r="H14" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I14" s="107">
         <f>G14-1.6*C13-0.6*D13-100</f>
         <v/>
       </c>
@@ -12884,14 +12884,14 @@
         </is>
       </c>
       <c r="G15" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H15" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I15" s="108">
+        <v>585.5</v>
+      </c>
+      <c r="H15" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I15" s="107">
         <f>G15-1.6*C14-0.6*D14-100</f>
         <v/>
       </c>
@@ -12933,14 +12933,14 @@
         </is>
       </c>
       <c r="G16" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H16" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I16" s="108">
+        <v>577.5</v>
+      </c>
+      <c r="H16" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I16" s="107">
         <f>G16-1.6*C15-0.6*D15-100</f>
         <v/>
       </c>
@@ -12982,14 +12982,14 @@
         </is>
       </c>
       <c r="G17" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H17" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I17" s="108">
+        <v>570</v>
+      </c>
+      <c r="H17" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I17" s="107">
         <f>G17-1.6*C16-0.6*D16-100</f>
         <v/>
       </c>
@@ -13031,14 +13031,14 @@
         </is>
       </c>
       <c r="G18" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H18" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I18" s="108">
+        <v>574.5</v>
+      </c>
+      <c r="H18" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I18" s="107">
         <f>G18-1.6*C17-0.6*D17-100</f>
         <v/>
       </c>
@@ -13080,14 +13080,14 @@
         </is>
       </c>
       <c r="G19" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H19" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I19" s="108">
+        <v>539</v>
+      </c>
+      <c r="H19" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I19" s="107">
         <f>G19-1.6*C18-0.6*D18-100</f>
         <v/>
       </c>
@@ -13129,14 +13129,14 @@
         </is>
       </c>
       <c r="G20" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H20" s="107" t="inlineStr">
-        <is>
-          <t>NC — nội suy</t>
-        </is>
-      </c>
-      <c r="I20" s="108">
+        <v>543.5</v>
+      </c>
+      <c r="H20" s="106" t="inlineStr">
+        <is>
+          <t>INV — median 3 tháng (SRRc1)</t>
+        </is>
+      </c>
+      <c r="I20" s="107">
         <f>G20-1.6*C19-0.6*D19-100</f>
         <v/>
       </c>
@@ -13178,14 +13178,14 @@
         </is>
       </c>
       <c r="G21" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H21" s="107" t="inlineStr">
+        <v>564.5</v>
+      </c>
+      <c r="H21" s="108" t="inlineStr">
         <is>
           <t>NC — nội suy</t>
         </is>
       </c>
-      <c r="I21" s="108">
+      <c r="I21" s="107">
         <f>G21-1.6*C20-0.6*D20-100</f>
         <v/>
       </c>
@@ -13227,14 +13227,14 @@
         </is>
       </c>
       <c r="G22" s="10" t="n">
-        <v>587.8</v>
-      </c>
-      <c r="H22" s="107" t="inlineStr">
+        <v>585.5</v>
+      </c>
+      <c r="H22" s="108" t="inlineStr">
         <is>
           <t>VN — neo nội địa (VSA/SteelOnline)</t>
         </is>
       </c>
-      <c r="I22" s="108">
+      <c r="I22" s="107">
         <f>G22-1.6*C21-0.6*D21-100</f>
         <v/>
       </c>
@@ -13254,7 +13254,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>GIÁ HIỆN TẠI — HRC/Than: investing.com (futures, fetch tự động); Quặng: World Bank Pink Sheet (tháng mới nhất (2026, 5), KHÔNG dùng investing.com — cùng phương pháp luận với 18 quý lịch sử, tránh lệch cơ sở futures-vs-spot); Thép XD: SteelOnline nội địa (ưu tiên) hoặc SRRc1 futures (dự phòng)</t>
+          <t>GIÁ HIỆN TẠI — HRC/Than: investing.com (futures, fetch tự động); Quặng: World Bank Pink Sheet (tháng mới nhất (2026, 6), KHÔNG dùng investing.com — cùng phương pháp luận với 18 quý lịch sử, tránh lệch cơ sở futures-vs-spot); Thép XD: SteelOnline nội địa (ưu tiên) hoặc SRRc1 futures (dự phòng)</t>
         </is>
       </c>
     </row>
@@ -13265,20 +13265,20 @@
         </is>
       </c>
       <c r="B25" s="110" t="n">
-        <v>475</v>
+        <v>461.5</v>
       </c>
       <c r="C25" s="110" t="n">
-        <v>108.64</v>
+        <v>100.8</v>
       </c>
       <c r="D25" s="110" t="n">
-        <v>220</v>
+        <v>226.8</v>
       </c>
       <c r="G25" s="110" t="n">
-        <v>577.1</v>
+        <v>574.8</v>
       </c>
       <c r="H25" s="94" t="inlineStr">
         <is>
-          <t>SteelOnline noi dia (15,120 dong/kg, quy doi ty gia 26,200)</t>
+          <t>SteelOnline noi dia (15,120 dong/kg, quy doi ty gia 26,303)</t>
         </is>
       </c>
     </row>
@@ -13589,35 +13589,35 @@
           <t>Spread Rebar (USD/t) — lag 1 quý/năm</t>
         </is>
       </c>
-      <c r="B36" s="108">
+      <c r="B36" s="107">
         <f>I5</f>
         <v/>
       </c>
-      <c r="C36" s="108">
+      <c r="C36" s="107">
         <f>MEDIAN(I6:I9)</f>
         <v/>
       </c>
-      <c r="D36" s="108">
+      <c r="D36" s="107">
         <f>MEDIAN(I10:I13)</f>
         <v/>
       </c>
-      <c r="E36" s="108">
+      <c r="E36" s="107">
         <f>MEDIAN(I14:I17)</f>
         <v/>
       </c>
-      <c r="F36" s="108">
+      <c r="F36" s="107">
         <f>MEDIAN(I18:I21)</f>
         <v/>
       </c>
-      <c r="G36" s="108">
+      <c r="G36" s="107">
         <f>MEDIAN(I22,I27)</f>
         <v/>
       </c>
-      <c r="H36" s="108">
+      <c r="H36" s="107">
         <f>H34-1.6*G32-0.6*G33-100</f>
         <v/>
       </c>
-      <c r="I36" s="108">
+      <c r="I36" s="107">
         <f>I34-1.6*H32-0.6*H33-100</f>
         <v/>
       </c>
@@ -14091,13 +14091,13 @@
         <v>11.84</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>10.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7" s="11">
         <f> EBIT / Doanh thu, EBIT = LN gộp - CP BH&amp;QLDN (khớp 04_PnL)</f>
@@ -14791,13 +14791,13 @@
         <v>26000</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>26200</v>
+        <v>26303</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>26724</v>
+        <v>26829</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>27258</v>
+        <v>27366</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -17449,13 +17449,13 @@
         <v>68000</v>
       </c>
       <c r="G26" s="39" t="n">
-        <v>82430</v>
+        <v>81925</v>
       </c>
       <c r="H26" s="39" t="n">
-        <v>88090</v>
+        <v>86643</v>
       </c>
       <c r="I26" s="39" t="n">
-        <v>87646</v>
+        <v>84399</v>
       </c>
     </row>
     <row r="27">
@@ -17511,13 +17511,13 @@
         <v>131220.010876575</v>
       </c>
       <c r="G28" s="39" t="n">
-        <v>152430</v>
+        <v>151925</v>
       </c>
       <c r="H28" s="39" t="n">
-        <v>166090</v>
+        <v>164643</v>
       </c>
       <c r="I28" s="39" t="n">
-        <v>174646</v>
+        <v>171399</v>
       </c>
     </row>
     <row r="29">

--- a/Bao cao/HPG/HPG_Model_2026-06.xlsx
+++ b/Bao cao/HPG/HPG_Model_2026-06.xlsx
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>03/07/2026 10:11</t>
+          <t>03/07/2026 12:14</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B31" s="35" t="inlineStr">
         <is>
-          <t>+12,759 tỷ</t>
+          <t>+12,753 tỷ</t>
         </is>
       </c>
       <c r="C31" s="74" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B33" s="35" t="inlineStr">
         <is>
-          <t>168,875 tỷ</t>
+          <t>168,869 tỷ</t>
         </is>
       </c>
       <c r="C33" s="74" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>+5,252 tỷ</t>
+          <t>+5,251 tỷ</t>
         </is>
       </c>
       <c r="C41" s="74" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B43" s="35" t="inlineStr">
         <is>
-          <t>20,705 tỷ</t>
+          <t>20,704 tỷ</t>
         </is>
       </c>
       <c r="C43" s="74" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C43" s="35" t="inlineStr">
         <is>
-          <t>KH 2026E NI: 20,705 tỷ</t>
+          <t>KH 2026E NI: 20,704 tỷ</t>
         </is>
       </c>
       <c r="D43" s="35" t="inlineStr">
@@ -13274,11 +13274,11 @@
         <v>226.8</v>
       </c>
       <c r="G25" s="110" t="n">
-        <v>574.8</v>
+        <v>574.9</v>
       </c>
       <c r="H25" s="94" t="inlineStr">
         <is>
-          <t>SteelOnline noi dia (15,120 dong/kg, quy doi ty gia 26,303)</t>
+          <t>SteelOnline noi dia (15,120 dong/kg, quy doi ty gia 26,302)</t>
         </is>
       </c>
     </row>
@@ -14791,13 +14791,13 @@
         <v>26000</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>26303</v>
+        <v>26302</v>
       </c>
       <c r="H25" s="10" t="n">
         <v>26829</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>27366</v>
+        <v>27365</v>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
@@ -17449,13 +17449,13 @@
         <v>68000</v>
       </c>
       <c r="G26" s="39" t="n">
-        <v>81925</v>
+        <v>81924</v>
       </c>
       <c r="H26" s="39" t="n">
-        <v>86643</v>
+        <v>86642</v>
       </c>
       <c r="I26" s="39" t="n">
-        <v>84399</v>
+        <v>84397</v>
       </c>
     </row>
     <row r="27">
@@ -17511,13 +17511,13 @@
         <v>131220.010876575</v>
       </c>
       <c r="G28" s="39" t="n">
-        <v>151925</v>
+        <v>151924</v>
       </c>
       <c r="H28" s="39" t="n">
-        <v>164643</v>
+        <v>164642</v>
       </c>
       <c r="I28" s="39" t="n">
-        <v>171399</v>
+        <v>171397</v>
       </c>
     </row>
     <row r="29">

--- a/Bao cao/HPG/HPG_Model_2026-06.xlsx
+++ b/Bao cao/HPG/HPG_Model_2026-06.xlsx
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>03/07/2026 12:14</t>
+          <t>03/07/2026 12:22</t>
         </is>
       </c>
     </row>
